--- a/Assets/Data/ShipData.xlsx
+++ b/Assets/Data/ShipData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAE\Year 2 Local\Game Design 2\Ghostly-Possessions-main\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D274F6-FC65-421B-A73D-9CECC53A7324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4037F8BD-9622-41D6-B92C-FC1C2FD7EF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{78A2007C-C672-409A-8041-24A311673B9F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ShipData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
-  <si>
-    <t>Ship ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="81">
   <si>
     <t>Ship Name</t>
   </si>
@@ -135,15 +132,9 @@
     <t>MaxSpeed</t>
   </si>
   <si>
-    <t>Ability Drain Rate Multiplier</t>
-  </si>
-  <si>
     <t>Rotation Speed</t>
   </si>
   <si>
-    <t>Crosshair ID</t>
-  </si>
-  <si>
     <t>Basic</t>
   </si>
   <si>
@@ -168,9 +159,6 @@
     <t>Enemy Health</t>
   </si>
   <si>
-    <t>Enemys Attack Speed</t>
-  </si>
-  <si>
     <t>Attack Speed</t>
   </si>
   <si>
@@ -258,7 +246,40 @@
     <t>0.33</t>
   </si>
   <si>
-    <t>ShipData</t>
+    <t>Internal Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosshair </t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Wave</t>
+  </si>
+  <si>
+    <t>Enemy Attack Speed</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>Guppy Blaster</t>
+  </si>
+  <si>
+    <t>Humpback</t>
+  </si>
+  <si>
+    <t>EVIL-Humpback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wavecrasher </t>
   </si>
 </sst>
 </file>
@@ -715,794 +736,762 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966BD3A6-413F-460B-8B75-8F3D95ECB740}">
-  <dimension ref="A1:DE26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="3"/>
-    <col min="5" max="5" width="18.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.77734375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.21875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" style="2" customWidth="1"/>
-    <col min="17" max="18" width="8.88671875" style="2"/>
-    <col min="19" max="19" width="8.88671875" style="3"/>
-    <col min="20" max="20" width="9.109375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="9.21875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="2" customWidth="1"/>
-    <col min="23" max="23" width="10.88671875" customWidth="1"/>
-    <col min="24" max="24" width="12.109375" customWidth="1"/>
-    <col min="25" max="25" width="12" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.77734375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="3"/>
+    <col min="4" max="4" width="18.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" style="2" customWidth="1"/>
+    <col min="15" max="16" width="8.88671875" style="2"/>
+    <col min="17" max="17" width="8.88671875" style="3"/>
+    <col min="18" max="18" width="9.109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="10.88671875" customWidth="1"/>
+    <col min="22" max="22" width="12.109375" customWidth="1"/>
+    <col min="23" max="23" width="12" style="2" customWidth="1"/>
+    <col min="24" max="24" width="12.77734375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="8.88671875" style="2"/>
+    <col min="26" max="26" width="11.33203125" style="2" customWidth="1"/>
     <col min="27" max="27" width="8.88671875" style="2"/>
-    <col min="28" max="28" width="11.33203125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="2"/>
-    <col min="30" max="30" width="11.5546875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="8.88671875" style="3"/>
+    <col min="28" max="28" width="11.5546875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="10" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" s="10" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>29</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q1" s="9" t="s">
         <v>44</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="U1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="W1" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="X1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC1" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="5">
+        <v>100</v>
+      </c>
+      <c r="I2" s="5">
+        <v>5</v>
+      </c>
+      <c r="J2" s="5">
+        <v>20</v>
+      </c>
+      <c r="K2" s="5">
+        <v>4</v>
+      </c>
+      <c r="L2" s="5">
+        <v>720</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>40</v>
+      </c>
+      <c r="P2" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="V1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z1" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF1" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG1" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="U2" s="5">
+        <v>20</v>
+      </c>
+      <c r="V2" s="5">
         <v>3</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="W2" s="5">
         <v>15</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>100</v>
-      </c>
-      <c r="J2" s="5">
-        <v>5</v>
-      </c>
-      <c r="K2" s="5">
-        <v>20</v>
-      </c>
-      <c r="L2" s="5">
-        <v>4</v>
-      </c>
-      <c r="M2" s="5">
-        <v>720</v>
-      </c>
-      <c r="N2" s="5">
-        <v>2</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>40</v>
-      </c>
-      <c r="R2" s="5">
-        <v>2</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="W2" s="5">
-        <v>20</v>
       </c>
       <c r="X2" s="5">
         <v>3</v>
       </c>
       <c r="Y2" s="5">
+        <v>240</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>12</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="5">
         <v>15</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="AD2" s="5">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AA2" s="5">
-        <v>240</v>
-      </c>
-      <c r="AB2" s="5">
-        <v>12</v>
-      </c>
-      <c r="AC2" s="5">
-        <v>5</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="5">
+      <c r="B3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="2">
+        <v>125</v>
+      </c>
+      <c r="I3" s="2">
+        <v>4</v>
+      </c>
+      <c r="J3" s="2">
         <v>15</v>
       </c>
-      <c r="AF2" s="5">
-        <v>2</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="K3" s="2">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="L3" s="2">
+        <v>720</v>
+      </c>
+      <c r="M3" s="2">
         <v>10</v>
       </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="N3" s="2">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2">
+        <v>40</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="2">
+        <v>45</v>
+      </c>
+      <c r="V3" s="2">
         <v>4</v>
       </c>
-      <c r="K3" s="2">
+      <c r="W3" s="2">
         <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4</v>
-      </c>
-      <c r="M3" s="2">
-        <v>720</v>
-      </c>
-      <c r="N3" s="2">
-        <v>3</v>
-      </c>
-      <c r="O3" s="2">
-        <v>10</v>
-      </c>
-      <c r="P3" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>40</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="W3" s="2">
-        <v>45</v>
       </c>
       <c r="X3" s="2">
         <v>4</v>
       </c>
       <c r="Y3" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>12</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="5">
+        <v>125</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5">
         <v>15</v>
       </c>
-      <c r="Z3" s="2">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>360</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>12</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD3" s="2">
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>720</v>
+      </c>
+      <c r="M4" s="5">
         <v>5</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF3" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>125</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>15</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>720</v>
       </c>
       <c r="N4" s="5">
         <v>3</v>
       </c>
       <c r="O4" s="5">
+        <v>40</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" s="5">
+        <v>40</v>
+      </c>
+      <c r="V4" s="5">
+        <v>7</v>
+      </c>
+      <c r="W4" s="5">
+        <v>8</v>
+      </c>
+      <c r="X4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>360</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>12</v>
+      </c>
+      <c r="AA4" s="5">
         <v>5</v>
       </c>
-      <c r="P4" s="5">
+      <c r="AB4" s="5">
         <v>3</v>
       </c>
-      <c r="Q4" s="5">
-        <v>40</v>
-      </c>
-      <c r="R4" s="5">
+      <c r="AC4" s="5">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="5">
         <v>2</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="W4" s="5">
-        <v>40</v>
-      </c>
-      <c r="X4" s="5">
+      <c r="AE4" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6</v>
+      </c>
+      <c r="J5" s="2">
+        <v>8</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>720</v>
+      </c>
+      <c r="M5" s="2">
+        <v>10</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="2">
+        <v>30</v>
+      </c>
+      <c r="V5" s="2">
+        <v>6</v>
+      </c>
+      <c r="W5" s="2">
+        <v>6</v>
+      </c>
+      <c r="X5" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>15</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5">
+        <v>125</v>
+      </c>
+      <c r="I6" s="5">
         <v>7</v>
-      </c>
-      <c r="Y4" s="5">
-        <v>8</v>
-      </c>
-      <c r="Z4" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="5">
-        <v>360</v>
-      </c>
-      <c r="AB4" s="5">
-        <v>12</v>
-      </c>
-      <c r="AC4" s="5">
-        <v>5</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>3</v>
-      </c>
-      <c r="AE4" s="5">
-        <v>15</v>
-      </c>
-      <c r="AF4" s="5">
-        <v>2</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2">
-        <v>90</v>
-      </c>
-      <c r="J5" s="2">
-        <v>6</v>
-      </c>
-      <c r="K5" s="2">
-        <v>8</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2</v>
-      </c>
-      <c r="M5" s="2">
-        <v>720</v>
-      </c>
-      <c r="N5" s="2">
-        <v>3</v>
-      </c>
-      <c r="O5" s="2">
-        <v>10</v>
-      </c>
-      <c r="P5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="W5" s="2">
-        <v>30</v>
-      </c>
-      <c r="X5" s="2">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>6</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>360</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>15</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="7">
-        <v>3</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="5">
-        <v>3</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="5">
-        <v>3</v>
-      </c>
-      <c r="I6" s="5">
-        <v>125</v>
       </c>
       <c r="J6" s="5">
         <v>7</v>
       </c>
       <c r="K6" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L6" s="5">
-        <v>4</v>
+        <v>480</v>
       </c>
       <c r="M6" s="5">
-        <v>480</v>
+        <v>25</v>
       </c>
       <c r="N6" s="5">
         <v>3</v>
       </c>
       <c r="O6" s="5">
-        <v>25</v>
-      </c>
-      <c r="P6" s="5">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="5">
         <v>0</v>
       </c>
+      <c r="P6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
       <c r="R6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" s="7">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="U6" s="5">
+        <v>45</v>
+      </c>
+      <c r="V6" s="5">
+        <v>2</v>
       </c>
       <c r="W6" s="5">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="X6" s="5">
         <v>2</v>
       </c>
       <c r="Y6" s="5">
+        <v>240</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>15</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="2">
+        <v>200</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2">
+        <v>7</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
+        <v>240</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="2">
+        <v>20</v>
+      </c>
+      <c r="O7" s="2">
+        <v>20</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="U7" s="2">
+        <v>65</v>
+      </c>
+      <c r="V7" s="2">
+        <v>4</v>
+      </c>
+      <c r="W7" s="2">
+        <v>9</v>
+      </c>
+      <c r="X7" s="2">
         <v>6</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Y7" s="2">
+        <v>120</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>14</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE7" s="3">
         <v>2</v>
       </c>
-      <c r="AA6" s="5">
-        <v>240</v>
-      </c>
-      <c r="AB6" s="5">
-        <v>15</v>
-      </c>
-      <c r="AC6" s="5">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="5">
-        <v>3</v>
-      </c>
-      <c r="AE6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG6" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="5">
+        <v>80</v>
+      </c>
+      <c r="I8" s="5">
         <v>8</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="2">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>200</v>
-      </c>
-      <c r="J7" s="2">
-        <v>8</v>
-      </c>
-      <c r="K7" s="2">
-        <v>7</v>
-      </c>
-      <c r="L7" s="2">
-        <v>4</v>
-      </c>
-      <c r="M7" s="2">
-        <v>240</v>
-      </c>
-      <c r="N7" s="2">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="J8" s="5">
         <v>20</v>
       </c>
-      <c r="Q7" s="2">
-        <v>20</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="W7" s="2">
-        <v>65</v>
-      </c>
-      <c r="X7" s="2">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>6</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>120</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>14</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>15</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="K8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="L8" s="5">
+        <v>720</v>
+      </c>
+      <c r="M8" s="5">
+        <v>5</v>
+      </c>
+      <c r="N8" s="5">
         <v>1</v>
       </c>
-      <c r="I8" s="5">
-        <v>80</v>
-      </c>
-      <c r="J8" s="5">
-        <v>8</v>
-      </c>
-      <c r="K8" s="5">
-        <v>20</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1</v>
-      </c>
-      <c r="M8" s="5">
-        <v>720</v>
-      </c>
-      <c r="N8" s="5">
-        <v>2</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="7"/>
+      <c r="O8" s="5">
+        <v>40</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
@@ -1512,16 +1501,73 @@
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="7"/>
-    </row>
-    <row r="10" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6"/>
+      <c r="AC8" s="7"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="2">
+        <v>250</v>
+      </c>
+      <c r="I9" s="2">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="2">
+        <v>120</v>
+      </c>
+      <c r="M9" s="2">
+        <v>20</v>
+      </c>
+      <c r="N9" s="2">
+        <v>30</v>
+      </c>
+      <c r="O9" s="2">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1533,26 +1579,24 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="7"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="7"/>
+      <c r="S10" s="5"/>
       <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
       <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="7"/>
-    </row>
-    <row r="12" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="6"/>
+      <c r="AC10" s="7"/>
+    </row>
+    <row r="12" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1564,26 +1608,24 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="7"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="7"/>
+      <c r="S12" s="5"/>
       <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="7"/>
-    </row>
-    <row r="14" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6"/>
+      <c r="AC12" s="7"/>
+    </row>
+    <row r="14" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1595,26 +1637,24 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="7"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="7"/>
+      <c r="S14" s="5"/>
       <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="7"/>
-    </row>
-    <row r="16" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="6"/>
+      <c r="AC14" s="7"/>
+    </row>
+    <row r="16" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -1626,26 +1666,24 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="7"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="7"/>
+      <c r="S16" s="5"/>
       <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5"/>
-      <c r="AE16" s="7"/>
-    </row>
-    <row r="18" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
+      <c r="AC16" s="7"/>
+    </row>
+    <row r="18" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -1657,26 +1695,24 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="7"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="7"/>
+      <c r="S18" s="5"/>
       <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="7"/>
-    </row>
-    <row r="20" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6"/>
+      <c r="AC18" s="7"/>
+    </row>
+    <row r="20" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -1688,26 +1724,24 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="7"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="7"/>
+      <c r="S20" s="5"/>
       <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
       <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="7"/>
-    </row>
-    <row r="22" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="6"/>
+      <c r="AC20" s="7"/>
+    </row>
+    <row r="22" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -1719,26 +1753,24 @@
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="7"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="7"/>
+      <c r="S22" s="5"/>
       <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="7"/>
-    </row>
-    <row r="24" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
+      <c r="AC22" s="7"/>
+    </row>
+    <row r="24" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -1750,26 +1782,24 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="7"/>
+      <c r="S24" s="5"/>
       <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="7"/>
-    </row>
-    <row r="26" spans="1:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
+      <c r="AC24" s="7"/>
+    </row>
+    <row r="26" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -1781,40 +1811,26 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="7"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="7"/>
+      <c r="S26" s="5"/>
       <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
       <c r="AB26" s="5"/>
-      <c r="AC26" s="5"/>
-      <c r="AD26" s="5"/>
-      <c r="AE26" s="7"/>
+      <c r="AC26" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"None"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7398B24E-709F-4369-96A7-5E6E36271163}">
-          <x14:formula1>
-            <xm:f>Sheet2!$A$2:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G8</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1828,32 +1844,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
